--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130294575</v>
+        <v>130294591</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>8440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636893</v>
+        <v>636884</v>
       </c>
       <c r="R8" t="n">
-        <v>6659138</v>
+        <v>6659043</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130294591</v>
+        <v>130294575</v>
       </c>
       <c r="B9" t="n">
-        <v>8440</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636884</v>
+        <v>636893</v>
       </c>
       <c r="R9" t="n">
-        <v>6659043</v>
+        <v>6659138</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130294567</v>
       </c>
       <c r="B3" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130294566</v>
       </c>
       <c r="B6" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130294591</v>
+        <v>130294575</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636884</v>
+        <v>636893</v>
       </c>
       <c r="R8" t="n">
-        <v>6659043</v>
+        <v>6659138</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130294575</v>
+        <v>130294591</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>8440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636893</v>
+        <v>636884</v>
       </c>
       <c r="R9" t="n">
-        <v>6659138</v>
+        <v>6659043</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1454,7 +1454,7 @@
         <v>130294577</v>
       </c>
       <c r="B10" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130294567</v>
       </c>
       <c r="B3" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130294569</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130294568</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130294566</v>
       </c>
       <c r="B6" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130294576</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130294575</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130294577</v>
       </c>
       <c r="B10" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130294572</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130294567</v>
       </c>
       <c r="B3" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130294566</v>
       </c>
       <c r="B6" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130294577</v>
       </c>
       <c r="B10" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130294567</v>
       </c>
       <c r="B3" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130294566</v>
       </c>
       <c r="B6" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130294575</v>
+        <v>130294591</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>8440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636893</v>
+        <v>636884</v>
       </c>
       <c r="R8" t="n">
-        <v>6659138</v>
+        <v>6659043</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130294591</v>
+        <v>130294575</v>
       </c>
       <c r="B9" t="n">
-        <v>8440</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636884</v>
+        <v>636893</v>
       </c>
       <c r="R9" t="n">
-        <v>6659043</v>
+        <v>6659138</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1454,7 +1454,7 @@
         <v>130294577</v>
       </c>
       <c r="B10" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130294567</v>
       </c>
       <c r="B3" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130294569</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130294568</v>
       </c>
       <c r="B5" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130294566</v>
       </c>
       <c r="B6" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130294576</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130294591</v>
+        <v>130294575</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636884</v>
+        <v>636893</v>
       </c>
       <c r="R8" t="n">
-        <v>6659043</v>
+        <v>6659138</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130294575</v>
+        <v>130294591</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>8440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636893</v>
+        <v>636884</v>
       </c>
       <c r="R9" t="n">
-        <v>6659138</v>
+        <v>6659043</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1454,7 +1454,7 @@
         <v>130294577</v>
       </c>
       <c r="B10" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130294572</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130294575</v>
+        <v>130294591</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>8440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636893</v>
+        <v>636884</v>
       </c>
       <c r="R8" t="n">
-        <v>6659138</v>
+        <v>6659043</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130294591</v>
+        <v>130294575</v>
       </c>
       <c r="B9" t="n">
-        <v>8440</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636884</v>
+        <v>636893</v>
       </c>
       <c r="R9" t="n">
-        <v>6659043</v>
+        <v>6659138</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1454,7 +1454,7 @@
         <v>130294577</v>
       </c>
       <c r="B10" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130294591</v>
+        <v>130294575</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636884</v>
+        <v>636893</v>
       </c>
       <c r="R8" t="n">
-        <v>6659043</v>
+        <v>6659138</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130294575</v>
+        <v>130294591</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>8440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636893</v>
+        <v>636884</v>
       </c>
       <c r="R9" t="n">
-        <v>6659138</v>
+        <v>6659043</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130294567</v>
       </c>
       <c r="B3" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130294569</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130294568</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130294566</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130294576</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130294575</v>
+        <v>130294591</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>8440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636893</v>
+        <v>636884</v>
       </c>
       <c r="R8" t="n">
-        <v>6659138</v>
+        <v>6659043</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130294591</v>
+        <v>130294575</v>
       </c>
       <c r="B9" t="n">
-        <v>8440</v>
+        <v>57859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636884</v>
+        <v>636893</v>
       </c>
       <c r="R9" t="n">
-        <v>6659043</v>
+        <v>6659138</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1454,7 +1454,7 @@
         <v>130294577</v>
       </c>
       <c r="B10" t="n">
-        <v>92220</v>
+        <v>92233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130294572</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130294567</v>
       </c>
       <c r="B3" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130294569</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130294568</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130294566</v>
       </c>
       <c r="B6" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130294576</v>
       </c>
       <c r="B7" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130294591</v>
+        <v>130294575</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636884</v>
+        <v>636893</v>
       </c>
       <c r="R8" t="n">
-        <v>6659043</v>
+        <v>6659138</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130294575</v>
+        <v>130294591</v>
       </c>
       <c r="B9" t="n">
-        <v>57859</v>
+        <v>8440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636893</v>
+        <v>636884</v>
       </c>
       <c r="R9" t="n">
-        <v>6659138</v>
+        <v>6659043</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1454,7 +1454,7 @@
         <v>130294577</v>
       </c>
       <c r="B10" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130294572</v>
       </c>
       <c r="B11" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130294567</v>
       </c>
       <c r="B3" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130294569</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130294568</v>
       </c>
       <c r="B5" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130294566</v>
       </c>
       <c r="B6" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130294576</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>130294575</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>130294577</v>
       </c>
       <c r="B10" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>130294572</v>
       </c>
       <c r="B11" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 56363-2025 artfynd.xlsx
+++ b/artfynd/A 56363-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130294564</v>
+        <v>130294566</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636907</v>
+        <v>636893</v>
       </c>
       <c r="R2" t="n">
-        <v>6659079</v>
+        <v>6659043</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -775,7 +775,7 @@
         <v>130294567</v>
       </c>
       <c r="B3" t="n">
-        <v>91776</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130294569</v>
+        <v>130294577</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636810</v>
+        <v>636894</v>
       </c>
       <c r="R4" t="n">
-        <v>6659063</v>
+        <v>6659041</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130294568</v>
+        <v>130294569</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636864</v>
+        <v>636810</v>
       </c>
       <c r="R5" t="n">
-        <v>6659175</v>
+        <v>6659063</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130294566</v>
+        <v>130294570</v>
       </c>
       <c r="B6" t="n">
-        <v>91776</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636893</v>
+        <v>636940</v>
       </c>
       <c r="R6" t="n">
-        <v>6659043</v>
+        <v>6659050</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,14 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130294576</v>
+        <v>130294572</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636910</v>
+        <v>636895</v>
       </c>
       <c r="R7" t="n">
-        <v>6659199</v>
+        <v>6658965</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130294575</v>
+        <v>130294573</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636893</v>
+        <v>636910</v>
       </c>
       <c r="R8" t="n">
-        <v>6659138</v>
+        <v>6658997</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130294591</v>
+        <v>130294574</v>
       </c>
       <c r="B9" t="n">
-        <v>8440</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636884</v>
+        <v>636925</v>
       </c>
       <c r="R9" t="n">
-        <v>6659043</v>
+        <v>6659021</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130294577</v>
+        <v>130294575</v>
       </c>
       <c r="B10" t="n">
-        <v>92235</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636894</v>
+        <v>636893</v>
       </c>
       <c r="R10" t="n">
-        <v>6659041</v>
+        <v>6659138</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1548,14 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130294572</v>
+        <v>130294576</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636895</v>
+        <v>636910</v>
       </c>
       <c r="R11" t="n">
-        <v>6658965</v>
+        <v>6659199</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1642,6 +1642,491 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130294584</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NV Lönnbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>636920</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6659040</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130294568</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NV Lönnbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>636864</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6659175</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130294564</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NV Lönnbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>636907</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6659079</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130294565</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NV Lönnbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>636951</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6659062</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130294591</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NV Lönnbacka, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>636884</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6659043</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
